--- a/sample_sov_addr_only.xlsx
+++ b/sample_sov_addr_only.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="SOV 2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cleaned Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Source References" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -816,16 +818,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>206200000</v>
       </c>
@@ -835,7 +832,1154 @@
       <c r="I10" t="n">
         <v>65100000</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>zip_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>insured_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>building_value</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>machinery_equipment_value</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>stock_supplies_value</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>bi_value</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bi_indemnity_period</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>occupancy_type</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>construction_class</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>year_built</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>building_height</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>number_of_floors</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>floor_area</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ambrosetti 2431, Munro, Buenos Aires, Argentina</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Munro, Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GlobalTech Inc</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>500 Industrial Blvd, Chicago, IL 60601, USA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>60601</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Pre-Eng Metal</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>45 High Street, London SW1A 1AA, United Kingdom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SW1A 1AA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TechnoLabs</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>2018</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gewerbering 2, 2440 Moosbrunn, Austria</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Moosbrunn</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bavaria Motors</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Masonry</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1995</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Krijgsbaan 247/D1, 9140 Temse, Belgium</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Temse</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9140</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BelgoChem</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Data Center</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Parque Industrial Manzano #3, Santa Cruz de la Sierra, Bolivia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Santa Cruz de la Sierra</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SantaCruz Mining</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BOB</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Pre-Eng Metal</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rua Barra Longa 11, Betim, Minas Gerais, Brazil</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Minas Gerais</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brasil Logistica</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Masonry</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>2012</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1200 Innovation Dr, Toronto, ON M5V 3L9, Canada</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>M5V 3L9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Maple Industries</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>zip_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>insured_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>building_value</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>machinery_equipment_value</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>stock_supplies_value</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>bi_value</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bi_indemnity_period</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>occupancy_type</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>construction_class</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>year_built</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>building_height</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>number_of_floors</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>floor_area</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D2</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E2</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F2</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I3</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D3</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E3</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F3</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D4</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E4</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F4</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F5</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I6</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D6</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E6</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F6</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D7</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E7</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F7</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J8</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G8</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I8</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D8</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E8</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F8</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J9</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G9</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I9</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D9</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E9</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F9</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
